--- a/packages/fixtures/files/showcase.xlsx
+++ b/packages/fixtures/files/showcase.xlsx
@@ -13,7 +13,11 @@
     <sheet name="Images" sheetId="6" r:id="rId6"/>
     <sheet name="Charts" sheetId="7" r:id="rId7"/>
     <sheet name="Comments" sheetId="8" r:id="rId8"/>
+    <sheet name="Tables" sheetId="9" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="UnitList">Units[Unit]</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -565,6 +569,29 @@
 </personList>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Units" displayName="Units" ref="A1:B5" totalsRowShown="0">
+  <autoFilter ref="A1:B5"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="Unit"/>
+    <tableColumn id="2" name="Meaning"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Readings" displayName="Readings" ref="A8:C13" totalsRowCount="1">
+  <autoFilter ref="A8:C12"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Parameter" totalsRowLabel="Total"/>
+    <tableColumn id="2" name="Value" totalsRowFunction="sum"/>
+    <tableColumn id="3" name="Unit"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="B3" dT="2026-09-30T10:00:00.00" personId="{1F0C2D1E-6A5B-4B1C-9E2F-0A1B2C3D4E5F}" id="{8C1B2A3D-4E5F-4061-8273-9A0B1C2D3E4F}">
@@ -1256,4 +1283,173 @@
   </sheetData>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mg/L</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">milligrams per litre</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ug/L</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">micrograms per litre</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ppm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parts per million</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parameter</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lead</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mg/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zinc</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>40</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ug/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moisture</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>12</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Copper</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ppm</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>SUM(B9:B12)</f>
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Unit" error="Pick a unit from the Units table" sqref="C9:C12">
+      <formula1>UnitList</formula1>
+    </dataValidation>
+  </dataValidations>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>